--- a/league_dict.xlsx
+++ b/league_dict.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8140BD0B-909A-4879-B1B8-9AF449A81F8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DD2A92-4156-492E-834B-EE838DF24B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
   <si>
     <t>Season</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>7qmc7ue3f8yzv8yqmsxc9irro</t>
+  </si>
+  <si>
+    <t>1t40s5vbbhc5bbkfiruh79mok</t>
+  </si>
+  <si>
+    <t>EFL Trophy</t>
   </si>
 </sst>
 </file>
@@ -653,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673AED86-F034-49DA-B6EF-799C1DFCCB2C}">
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -1167,6 +1173,17 @@
         <v>75</v>
       </c>
     </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s">
+        <v>80</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/league_dict.xlsx
+++ b/league_dict.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wt_an\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90DD2A92-4156-492E-834B-EE838DF24B62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65338971-725D-4B5C-8448-C7467A1B44C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E870964E-72B7-432A-AC57-81E8B1FB7B9A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="128">
   <si>
     <t>Season</t>
   </si>
@@ -282,6 +282,144 @@
   </si>
   <si>
     <t>EFL Trophy</t>
+  </si>
+  <si>
+    <t>leagueid</t>
+  </si>
+  <si>
+    <t>ENG1</t>
+  </si>
+  <si>
+    <t>ENG2</t>
+  </si>
+  <si>
+    <t>ENG3</t>
+  </si>
+  <si>
+    <t>ENG4</t>
+  </si>
+  <si>
+    <t>FAC</t>
+  </si>
+  <si>
+    <t>LC</t>
+  </si>
+  <si>
+    <t>SCO1</t>
+  </si>
+  <si>
+    <t>SPA1</t>
+  </si>
+  <si>
+    <t>SPA2</t>
+  </si>
+  <si>
+    <t>FRA1</t>
+  </si>
+  <si>
+    <t>FRA2</t>
+  </si>
+  <si>
+    <t>GER1</t>
+  </si>
+  <si>
+    <t>GER2</t>
+  </si>
+  <si>
+    <t>POR1</t>
+  </si>
+  <si>
+    <t>GRE1</t>
+  </si>
+  <si>
+    <t>ITA1</t>
+  </si>
+  <si>
+    <t>ITA2</t>
+  </si>
+  <si>
+    <t>SWI1</t>
+  </si>
+  <si>
+    <t>AUT1</t>
+  </si>
+  <si>
+    <t>UCL</t>
+  </si>
+  <si>
+    <t>EUL</t>
+  </si>
+  <si>
+    <t>ECL</t>
+  </si>
+  <si>
+    <t>BEL1</t>
+  </si>
+  <si>
+    <t>AUS1</t>
+  </si>
+  <si>
+    <t>DEN1</t>
+  </si>
+  <si>
+    <t>NED1</t>
+  </si>
+  <si>
+    <t>IRE1</t>
+  </si>
+  <si>
+    <t>JAP1</t>
+  </si>
+  <si>
+    <t>SWE1</t>
+  </si>
+  <si>
+    <t>FIN1</t>
+  </si>
+  <si>
+    <t>NED2</t>
+  </si>
+  <si>
+    <t>NOR1</t>
+  </si>
+  <si>
+    <t>SuperLig</t>
+  </si>
+  <si>
+    <t>TUR1</t>
+  </si>
+  <si>
+    <t>e00dq6lfzgc7vo631cz8ktc0k</t>
+  </si>
+  <si>
+    <t>7wshhtqrzmwrkkygjqf9l0idw</t>
+  </si>
+  <si>
+    <t>UEFA Nations League</t>
+  </si>
+  <si>
+    <t>34dybyk5aptjukvigl3q7zi8k</t>
+  </si>
+  <si>
+    <t>UEFA U21 Qualifiers</t>
+  </si>
+  <si>
+    <t>2vj8sd86i396edjnxg4uojyms</t>
+  </si>
+  <si>
+    <t>AFCON Qualifiers</t>
+  </si>
+  <si>
+    <t>3lblvo39e164lm8jjkz9uuu50</t>
+  </si>
+  <si>
+    <t>Kirin Cup</t>
+  </si>
+  <si>
+    <t>dezv8l0fzgcxtejl0dwmy1gyc</t>
+  </si>
+  <si>
+    <t>International Friendly</t>
   </si>
 </sst>
 </file>
@@ -659,14 +797,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{673AED86-F034-49DA-B6EF-799C1DFCCB2C}">
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -679,8 +817,11 @@
       <c r="D1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>45</v>
       </c>
@@ -693,8 +834,11 @@
       <c r="D2">
         <v>47</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
@@ -707,8 +851,11 @@
       <c r="D3">
         <v>48</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -721,8 +868,11 @@
       <c r="D4">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -735,8 +885,11 @@
       <c r="D5">
         <v>109</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>45</v>
       </c>
@@ -749,8 +902,11 @@
       <c r="D6">
         <v>132</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -763,8 +919,11 @@
       <c r="D7">
         <v>133</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -777,8 +936,11 @@
       <c r="D8">
         <v>64</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -791,8 +953,11 @@
       <c r="D9">
         <v>87</v>
       </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E9" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
@@ -802,8 +967,11 @@
       <c r="C10" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>45</v>
       </c>
@@ -816,8 +984,11 @@
       <c r="D11">
         <v>53</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>45</v>
       </c>
@@ -827,8 +998,11 @@
       <c r="C12" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -841,8 +1015,11 @@
       <c r="D13">
         <v>54</v>
       </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E13" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>45</v>
       </c>
@@ -855,8 +1032,11 @@
       <c r="D14">
         <v>146</v>
       </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>45</v>
       </c>
@@ -869,8 +1049,11 @@
       <c r="D15">
         <v>61</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -880,8 +1063,11 @@
       <c r="C16" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>45</v>
       </c>
@@ -894,8 +1080,11 @@
       <c r="D17">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>45</v>
       </c>
@@ -905,8 +1094,11 @@
       <c r="C18" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E18" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -919,8 +1111,11 @@
       <c r="D19">
         <v>69</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E19" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>45</v>
       </c>
@@ -933,8 +1128,11 @@
       <c r="D20">
         <v>38</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -947,8 +1145,11 @@
       <c r="D21">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>45</v>
       </c>
@@ -961,8 +1162,11 @@
       <c r="D22">
         <v>73</v>
       </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>45</v>
       </c>
@@ -975,8 +1179,11 @@
       <c r="D23">
         <v>10216</v>
       </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E23" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -989,8 +1196,11 @@
       <c r="D24">
         <v>40</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -1004,7 +1214,7 @@
         <v>10611</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -1017,8 +1227,11 @@
       <c r="D26">
         <v>113</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>45</v>
       </c>
@@ -1031,8 +1244,11 @@
       <c r="D27">
         <v>46</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E27" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>45</v>
       </c>
@@ -1046,7 +1262,7 @@
         <v>10613</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>45</v>
       </c>
@@ -1060,7 +1276,7 @@
         <v>10615</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>2026</v>
       </c>
@@ -1071,7 +1287,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>2026</v>
       </c>
@@ -1085,7 +1301,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>2026</v>
       </c>
@@ -1096,7 +1312,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>45</v>
       </c>
@@ -1106,8 +1322,11 @@
       <c r="C33" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>2026</v>
       </c>
@@ -1117,8 +1336,11 @@
       <c r="C34" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>2026</v>
       </c>
@@ -1128,8 +1350,11 @@
       <c r="C35" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>2026</v>
       </c>
@@ -1139,8 +1364,11 @@
       <c r="C36" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>2026</v>
       </c>
@@ -1150,8 +1378,11 @@
       <c r="C37" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>2026</v>
       </c>
@@ -1161,8 +1392,11 @@
       <c r="C38" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E38" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>2026</v>
       </c>
@@ -1172,8 +1406,11 @@
       <c r="C39" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="E39" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>45</v>
       </c>
@@ -1182,6 +1419,75 @@
       </c>
       <c r="C40" t="s">
         <v>80</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" t="s">
+        <v>117</v>
+      </c>
+      <c r="E41" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>119</v>
+      </c>
+      <c r="C42" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" t="s">
+        <v>121</v>
+      </c>
+      <c r="C43" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C44" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>127</v>
+      </c>
+      <c r="C46" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>
